--- a/Assets/Stage00.xlsx
+++ b/Assets/Stage00.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GE2A09\PG\MyFirstGame\assets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GE2A09\PG\GolfGame\Assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFD2F048-1D24-4179-B0D8-413E477672DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE371402-7431-482A-B5EC-D1A7F08843F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5150F55E-DCA2-4F5E-90F9-383F0C3F5E47}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8880" xr2:uid="{5150F55E-DCA2-4F5E-90F9-383F0C3F5E47}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5444374-3490-4F52-B93E-5093D8A0761D}">
-  <dimension ref="A1:R20"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="3.19921875" bestFit="1" customWidth="1"/>
@@ -460,7 +460,7 @@
     <col min="17" max="18" width="2.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1">
         <v>1</v>
       </c>
@@ -497,26 +497,8 @@
       <c r="L1">
         <v>1</v>
       </c>
-      <c r="M1">
-        <v>0</v>
-      </c>
-      <c r="N1">
-        <v>0</v>
-      </c>
-      <c r="O1">
-        <v>0</v>
-      </c>
-      <c r="P1">
-        <v>0</v>
-      </c>
-      <c r="Q1">
-        <v>0</v>
-      </c>
-      <c r="R1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>0</v>
       </c>
@@ -553,26 +535,8 @@
       <c r="L2">
         <v>1</v>
       </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>-1</v>
       </c>
@@ -609,26 +573,8 @@
       <c r="L3">
         <v>1</v>
       </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-      <c r="R3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>-1</v>
       </c>
@@ -665,26 +611,8 @@
       <c r="L4">
         <v>1</v>
       </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
-      <c r="R4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>-1</v>
       </c>
@@ -721,26 +649,8 @@
       <c r="L5">
         <v>1</v>
       </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>0</v>
-      </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-      <c r="R5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>0</v>
       </c>
@@ -777,26 +687,8 @@
       <c r="L6">
         <v>1</v>
       </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-      <c r="R6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>1</v>
       </c>
@@ -833,26 +725,8 @@
       <c r="L7">
         <v>1</v>
       </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-      <c r="R7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>1</v>
       </c>
@@ -889,26 +763,8 @@
       <c r="L8">
         <v>1</v>
       </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-      <c r="R8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>1</v>
       </c>
@@ -945,26 +801,8 @@
       <c r="L9">
         <v>1</v>
       </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-      <c r="R9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>1</v>
       </c>
@@ -1001,26 +839,8 @@
       <c r="L10">
         <v>1</v>
       </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-      <c r="R10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>1</v>
       </c>
@@ -1057,26 +877,8 @@
       <c r="L11">
         <v>1</v>
       </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
-        <v>0</v>
-      </c>
-      <c r="Q11">
-        <v>0</v>
-      </c>
-      <c r="R11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>1</v>
       </c>
@@ -1111,472 +913,6 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>1</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
-      <c r="P12">
-        <v>0</v>
-      </c>
-      <c r="Q12">
-        <v>0</v>
-      </c>
-      <c r="R12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A13">
-        <v>1</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
-      <c r="P13">
-        <v>0</v>
-      </c>
-      <c r="Q13">
-        <v>0</v>
-      </c>
-      <c r="R13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A14">
-        <v>1</v>
-      </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14">
-        <v>0</v>
-      </c>
-      <c r="P14">
-        <v>0</v>
-      </c>
-      <c r="Q14">
-        <v>0</v>
-      </c>
-      <c r="R14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A15">
-        <v>1</v>
-      </c>
-      <c r="B15">
-        <v>0</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15">
-        <v>0</v>
-      </c>
-      <c r="P15">
-        <v>0</v>
-      </c>
-      <c r="Q15">
-        <v>0</v>
-      </c>
-      <c r="R15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A16">
-        <v>1</v>
-      </c>
-      <c r="B16">
-        <v>0</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16">
-        <v>0</v>
-      </c>
-      <c r="P16">
-        <v>0</v>
-      </c>
-      <c r="Q16">
-        <v>0</v>
-      </c>
-      <c r="R16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A17">
-        <v>1</v>
-      </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <v>0</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17">
-        <v>0</v>
-      </c>
-      <c r="P17">
-        <v>0</v>
-      </c>
-      <c r="Q17">
-        <v>0</v>
-      </c>
-      <c r="R17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A18">
-        <v>1</v>
-      </c>
-      <c r="B18">
-        <v>0</v>
-      </c>
-      <c r="C18">
-        <v>0</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18">
-        <v>0</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
-      <c r="O18">
-        <v>0</v>
-      </c>
-      <c r="P18">
-        <v>0</v>
-      </c>
-      <c r="Q18">
-        <v>0</v>
-      </c>
-      <c r="R18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A19">
-        <v>1</v>
-      </c>
-      <c r="B19">
-        <v>0</v>
-      </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19">
-        <v>0</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="O19">
-        <v>0</v>
-      </c>
-      <c r="P19">
-        <v>0</v>
-      </c>
-      <c r="Q19">
-        <v>0</v>
-      </c>
-      <c r="R19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A20">
-        <v>1</v>
-      </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-      <c r="C20">
-        <v>0</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20">
-        <v>0</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20">
-        <v>0</v>
-      </c>
-      <c r="P20">
-        <v>0</v>
-      </c>
-      <c r="Q20">
-        <v>0</v>
-      </c>
-      <c r="R20">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Stage00.xlsx
+++ b/Assets/Stage00.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GE2A09\PG\GolfGame\Assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE371402-7431-482A-B5EC-D1A7F08843F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3D63553-5266-4BDC-9507-F74C4AEEAED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8880" xr2:uid="{5150F55E-DCA2-4F5E-90F9-383F0C3F5E47}"/>
+    <workbookView xWindow="42945" yWindow="5760" windowWidth="17280" windowHeight="8880" xr2:uid="{5150F55E-DCA2-4F5E-90F9-383F0C3F5E47}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,6 +33,15 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="1">
+  <si>
+    <t>n</t>
+    <phoneticPr fontId="1"/>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -447,20 +456,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5444374-3490-4F52-B93E-5093D8A0761D}">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="3.19921875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="3.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.19921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="2.3984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="3.3984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="15" width="2.3984375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="3.3984375" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="2.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.3984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="9" width="3.19921875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="2.3984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="18" width="3.3984375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="2.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A1">
         <v>1</v>
       </c>
@@ -497,8 +506,29 @@
       <c r="L1">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M1">
+        <v>0</v>
+      </c>
+      <c r="N1">
+        <v>0</v>
+      </c>
+      <c r="O1">
+        <v>0</v>
+      </c>
+      <c r="P1">
+        <v>0</v>
+      </c>
+      <c r="Q1">
+        <v>0</v>
+      </c>
+      <c r="R1">
+        <v>1</v>
+      </c>
+      <c r="S1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>0</v>
       </c>
@@ -535,10 +565,31 @@
       <c r="L2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>1</v>
+      </c>
+      <c r="S2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="B3">
         <v>-1</v>
@@ -547,7 +598,7 @@
         <v>-1</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -573,19 +624,40 @@
       <c r="L3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>1</v>
+      </c>
+      <c r="S3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A4">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="B4">
+        <v>-1</v>
+      </c>
+      <c r="C4">
         <v>10</v>
       </c>
-      <c r="C4">
-        <v>-1</v>
-      </c>
       <c r="D4">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -611,10 +683,31 @@
       <c r="L4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>1</v>
+      </c>
+      <c r="S4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A5">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="B5">
         <v>-1</v>
@@ -623,7 +716,7 @@
         <v>-1</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -649,8 +742,29 @@
       <c r="L5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>1</v>
+      </c>
+      <c r="S5" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>0</v>
       </c>
@@ -687,8 +801,29 @@
       <c r="L6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>1</v>
+      </c>
+      <c r="S6" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>1</v>
       </c>
@@ -720,13 +855,34 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
+        <v>-1</v>
+      </c>
+      <c r="M7">
+        <v>-1</v>
+      </c>
+      <c r="N7">
+        <v>-1</v>
+      </c>
+      <c r="O7">
+        <v>-1</v>
+      </c>
+      <c r="P7">
+        <v>-1</v>
+      </c>
+      <c r="Q7">
+        <v>-1</v>
+      </c>
+      <c r="R7">
+        <v>-1</v>
+      </c>
+      <c r="S7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>1</v>
       </c>
@@ -740,31 +896,52 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>1</v>
+      </c>
+      <c r="S8" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>1</v>
       </c>
@@ -775,34 +952,55 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>1</v>
+      </c>
+      <c r="S9" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>1</v>
       </c>
@@ -816,31 +1014,52 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J10">
         <v>1</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>1</v>
+      </c>
+      <c r="S10" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>1</v>
       </c>
@@ -854,71 +1073,644 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>-1</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>1</v>
+      </c>
+      <c r="S11" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A12">
+        <v>1</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>-1</v>
+      </c>
+      <c r="F12">
+        <v>-1</v>
+      </c>
+      <c r="G12">
+        <v>-1</v>
+      </c>
+      <c r="H12">
+        <v>-1</v>
+      </c>
+      <c r="I12">
+        <v>-1</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>-1</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>1</v>
+      </c>
+      <c r="S12" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A13">
+        <v>1</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>-1</v>
+      </c>
+      <c r="L13">
+        <v>-1</v>
+      </c>
+      <c r="M13">
+        <v>-1</v>
+      </c>
+      <c r="N13">
+        <v>-1</v>
+      </c>
+      <c r="O13">
+        <v>-1</v>
+      </c>
+      <c r="P13">
+        <v>-1</v>
+      </c>
+      <c r="Q13">
+        <v>-1</v>
+      </c>
+      <c r="R13">
+        <v>-1</v>
+      </c>
+      <c r="S13" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <v>1</v>
+      </c>
+      <c r="N14">
+        <v>1</v>
+      </c>
+      <c r="O14">
+        <v>1</v>
+      </c>
+      <c r="P14">
+        <v>1</v>
+      </c>
+      <c r="Q14">
+        <v>1</v>
+      </c>
+      <c r="R14">
+        <v>1</v>
+      </c>
+      <c r="S14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A15">
+        <v>1</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>1</v>
+      </c>
+      <c r="S15" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A16">
+        <v>1</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>1</v>
+      </c>
+      <c r="S16" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A17">
+        <v>1</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>1</v>
+      </c>
+      <c r="S17" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A18">
+        <v>1</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
         <v>11</v>
       </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A12">
-        <v>1</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <v>1</v>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>1</v>
+      </c>
+      <c r="S18" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A19">
+        <v>1</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>1</v>
+      </c>
+      <c r="S19" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A20">
+        <v>1</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20">
+        <v>1</v>
+      </c>
+      <c r="M20">
+        <v>1</v>
+      </c>
+      <c r="N20">
+        <v>1</v>
+      </c>
+      <c r="O20">
+        <v>1</v>
+      </c>
+      <c r="P20">
+        <v>1</v>
+      </c>
+      <c r="Q20">
+        <v>1</v>
+      </c>
+      <c r="R20">
+        <v>1</v>
+      </c>
+      <c r="S20" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B21" t="s">
+        <v>0</v>
+      </c>
+      <c r="C21" t="s">
+        <v>0</v>
+      </c>
+      <c r="D21" t="s">
+        <v>0</v>
+      </c>
+      <c r="E21" t="s">
+        <v>0</v>
+      </c>
+      <c r="F21" t="s">
+        <v>0</v>
+      </c>
+      <c r="G21" t="s">
+        <v>0</v>
+      </c>
+      <c r="H21" t="s">
+        <v>0</v>
+      </c>
+      <c r="I21" t="s">
+        <v>0</v>
+      </c>
+      <c r="J21" t="s">
+        <v>0</v>
+      </c>
+      <c r="K21" t="s">
+        <v>0</v>
+      </c>
+      <c r="L21" t="s">
+        <v>0</v>
+      </c>
+      <c r="M21" t="s">
+        <v>0</v>
+      </c>
+      <c r="N21" t="s">
+        <v>0</v>
+      </c>
+      <c r="O21" t="s">
+        <v>0</v>
+      </c>
+      <c r="P21" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>0</v>
+      </c>
+      <c r="R21" t="s">
+        <v>0</v>
+      </c>
+      <c r="S21" t="s">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="A1:XFD1048576">
+  <conditionalFormatting sqref="A1:R20 T1:XFD21 A20:S20 S21 A22:XFD1048576">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>-1</formula>
     </cfRule>

--- a/Assets/Stage00.xlsx
+++ b/Assets/Stage00.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GE2A09\PG\GolfGame\Assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3D63553-5266-4BDC-9507-F74C4AEEAED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C016409D-0897-4595-A461-F227A720C572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="42945" yWindow="5760" windowWidth="17280" windowHeight="8880" xr2:uid="{5150F55E-DCA2-4F5E-90F9-383F0C3F5E47}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5150F55E-DCA2-4F5E-90F9-383F0C3F5E47}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -93,7 +93,7 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
     <dxf>
       <fill>
         <patternFill>
@@ -123,6 +123,13 @@
       <fill>
         <patternFill>
           <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -463,8 +470,7 @@
     <col min="2" max="2" width="3.3984375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="3.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="3.3984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="9" width="3.19921875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="2.3984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="3.19921875" bestFit="1" customWidth="1"/>
     <col min="11" max="18" width="3.3984375" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="2.3984375" bestFit="1" customWidth="1"/>
   </cols>
@@ -1306,7 +1312,7 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1418,16 +1424,16 @@
         <v>1</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1498,7 +1504,7 @@
         <v>0</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -1557,7 +1563,7 @@
         <v>0</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -1711,16 +1717,19 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="A1:R20 T1:XFD21 A20:S20 S21 A22:XFD1048576">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+      <formula>21</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
       <formula>-1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>11</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
       <formula>10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Assets/Stage00.xlsx
+++ b/Assets/Stage00.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GE2A09\PG\GolfGame\Assets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GE3A09\PG\golfgame\Assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C016409D-0897-4595-A461-F227A720C572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B584A6BD-0989-4790-A7BF-0FF61824AA33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5150F55E-DCA2-4F5E-90F9-383F0C3F5E47}"/>
+    <workbookView xWindow="40695" yWindow="4440" windowWidth="17280" windowHeight="8880" xr2:uid="{5150F55E-DCA2-4F5E-90F9-383F0C3F5E47}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -93,7 +93,53 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="11">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor auto="1"/>
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -470,7 +516,9 @@
     <col min="2" max="2" width="3.3984375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="3.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="3.3984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="3.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.19921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="3.19921875" bestFit="1" customWidth="1"/>
     <col min="11" max="18" width="3.3984375" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="2.3984375" bestFit="1" customWidth="1"/>
   </cols>
@@ -728,7 +776,7 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1717,20 +1765,23 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="A1:R20 T1:XFD21 A20:S20 S21 A22:XFD1048576">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
       <formula>21</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
       <formula>-1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
       <formula>11</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
       <formula>10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
       <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
+      <formula>22</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
